--- a/DCU.xlsx
+++ b/DCU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00905BDB-DB2F-4CEC-B971-07665059CBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D34C01-240A-4524-8165-F3BAF353636A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="413">
   <si>
     <t>id</t>
   </si>
@@ -1269,6 +1269,12 @@
   </si>
   <si>
     <t>OutKast</t>
+  </si>
+  <si>
+    <t>The Weenie</t>
+  </si>
+  <si>
+    <t>Summer, 2016</t>
   </si>
 </sst>
 </file>
@@ -2568,10 +2574,10 @@
         <v>46264</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="K21" t="s">
         <v>196</v>
@@ -2694,93 +2700,96 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>250</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C24">
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>245</v>
+      </c>
+      <c r="E24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" t="s">
+        <v>411</v>
       </c>
       <c r="G24">
-        <v>242</v>
+        <v>52</v>
       </c>
       <c r="H24" s="1">
-        <v>43056</v>
+        <v>46271</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="K24" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="M24" t="s">
-        <v>101</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s">
-        <v>20</v>
-      </c>
-      <c r="O24" t="s">
-        <v>282</v>
+        <v>125</v>
       </c>
       <c r="P24" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="Q24" t="s">
-        <v>102</v>
+        <v>247</v>
       </c>
       <c r="R24" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B25">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="H25" s="1">
-        <v>43455</v>
+        <v>43056</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="K25" t="s">
         <v>18</v>
       </c>
       <c r="M25" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N25" t="s">
         <v>20</v>
       </c>
       <c r="O25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P25" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q25" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="R25" t="s">
         <v>22</v>
@@ -2788,46 +2797,46 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B26">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G26">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H26" s="1">
-        <v>43560</v>
+        <v>43455</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="K26" t="s">
         <v>18</v>
       </c>
       <c r="M26" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="N26" t="s">
         <v>20</v>
       </c>
       <c r="O26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q26" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="R26" t="s">
         <v>22</v>
@@ -2835,46 +2844,46 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B27">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G27">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="H27" s="1">
-        <v>43868</v>
+        <v>43560</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K27" t="s">
         <v>18</v>
       </c>
       <c r="M27" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N27" t="s">
         <v>20</v>
       </c>
       <c r="O27" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P27" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="Q27" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="R27" t="s">
         <v>22</v>
@@ -2882,46 +2891,46 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B28">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G28">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="H28" s="1">
-        <v>44407</v>
+        <v>43868</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="K28" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="M28" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N28" t="s">
         <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P28" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q28" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="R28" t="s">
         <v>22</v>
@@ -2929,60 +2938,57 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
-      </c>
-      <c r="E29" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G29">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="H29" s="1">
-        <v>44574</v>
+        <v>44407</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K29" t="s">
         <v>117</v>
       </c>
       <c r="M29" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="N29" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="O29" t="s">
+        <v>288</v>
       </c>
       <c r="P29" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="Q29" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="R29" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30">
         <v>29</v>
@@ -2991,13 +2997,13 @@
         <v>121</v>
       </c>
       <c r="E30" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G30">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H30" s="1">
         <v>44574</v>
@@ -3018,7 +3024,7 @@
         <v>125</v>
       </c>
       <c r="P30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q30" t="s">
         <v>126</v>
@@ -3029,10 +3035,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B31">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -3041,13 +3047,13 @@
         <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G31">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H31" s="1">
         <v>44574</v>
@@ -3068,7 +3074,7 @@
         <v>125</v>
       </c>
       <c r="P31" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q31" t="s">
         <v>126</v>
@@ -3079,10 +3085,10 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -3091,16 +3097,16 @@
         <v>121</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F32" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G32">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H32" s="1">
-        <v>44581</v>
+        <v>44574</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>395</v>
@@ -3118,7 +3124,7 @@
         <v>125</v>
       </c>
       <c r="P32" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q32" t="s">
         <v>126</v>
@@ -3129,10 +3135,10 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -3141,16 +3147,16 @@
         <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F33" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G33">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H33" s="1">
-        <v>44588</v>
+        <v>44581</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>395</v>
@@ -3168,7 +3174,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q33" t="s">
         <v>126</v>
@@ -3179,10 +3185,10 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B34">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -3191,16 +3197,16 @@
         <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F34" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G34">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H34" s="1">
-        <v>44595</v>
+        <v>44588</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>395</v>
@@ -3218,7 +3224,7 @@
         <v>125</v>
       </c>
       <c r="P34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q34" t="s">
         <v>126</v>
@@ -3229,10 +3235,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B35">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -3241,16 +3247,16 @@
         <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F35" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G35">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H35" s="1">
-        <v>44602</v>
+        <v>44595</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>395</v>
@@ -3268,7 +3274,7 @@
         <v>125</v>
       </c>
       <c r="P35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q35" t="s">
         <v>126</v>
@@ -3279,10 +3285,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B36">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -3291,16 +3297,16 @@
         <v>121</v>
       </c>
       <c r="E36" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F36" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G36">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H36" s="1">
-        <v>44609</v>
+        <v>44602</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>395</v>
@@ -3318,7 +3324,7 @@
         <v>125</v>
       </c>
       <c r="P36" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q36" t="s">
         <v>126</v>
@@ -3329,87 +3335,93 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B37">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C37">
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>121</v>
+      </c>
+      <c r="E37" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" t="s">
+        <v>148</v>
+      </c>
+      <c r="G37">
+        <v>45</v>
       </c>
       <c r="H37" s="1">
-        <v>44855</v>
+        <v>44609</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="K37" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="M37" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="N37" t="s">
-        <v>20</v>
-      </c>
-      <c r="O37" t="s">
-        <v>290</v>
+        <v>125</v>
       </c>
       <c r="P37" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="Q37" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="R37" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B38">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H38" s="1">
-        <v>45002</v>
+        <v>44855</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K38" t="s">
         <v>18</v>
       </c>
       <c r="M38" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N38" t="s">
         <v>20</v>
       </c>
       <c r="O38" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P38" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="Q38" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="R38" t="s">
         <v>22</v>
@@ -3417,43 +3429,43 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B39">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H39" s="1">
-        <v>45093</v>
+        <v>45002</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K39" t="s">
         <v>18</v>
       </c>
       <c r="M39" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N39" t="s">
         <v>20</v>
       </c>
       <c r="O39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P39" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="Q39" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="R39" t="s">
         <v>22</v>
@@ -3461,43 +3473,43 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B40">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H40" s="1">
-        <v>44624</v>
+        <v>45093</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K40" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="M40" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="N40" t="s">
         <v>20</v>
       </c>
       <c r="O40" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="P40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q40" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="R40" t="s">
         <v>22</v>
@@ -3505,57 +3517,54 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B41">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" t="s">
-        <v>122</v>
-      </c>
-      <c r="F41" t="s">
-        <v>168</v>
-      </c>
-      <c r="G41">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="H41" s="1">
-        <v>45555</v>
+        <v>44624</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="K41" t="s">
         <v>163</v>
       </c>
       <c r="M41" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N41" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="O41" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="P41" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="Q41" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="R41" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B42">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42">
         <v>41</v>
@@ -3564,16 +3573,16 @@
         <v>167</v>
       </c>
       <c r="E42" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F42" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G42">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H42" s="1">
-        <v>45565</v>
+        <v>45555</v>
       </c>
       <c r="K42" t="s">
         <v>163</v>
@@ -3588,7 +3597,7 @@
         <v>302</v>
       </c>
       <c r="P42" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q42" t="s">
         <v>170</v>
@@ -3599,10 +3608,10 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B43">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -3611,16 +3620,16 @@
         <v>167</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F43" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G43">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H43" s="1">
-        <v>45572</v>
+        <v>45565</v>
       </c>
       <c r="K43" t="s">
         <v>163</v>
@@ -3635,7 +3644,7 @@
         <v>302</v>
       </c>
       <c r="P43" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q43" t="s">
         <v>170</v>
@@ -3646,10 +3655,10 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B44">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -3658,16 +3667,16 @@
         <v>167</v>
       </c>
       <c r="E44" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F44" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G44">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H44" s="1">
-        <v>45579</v>
+        <v>45572</v>
       </c>
       <c r="K44" t="s">
         <v>163</v>
@@ -3682,7 +3691,7 @@
         <v>302</v>
       </c>
       <c r="P44" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q44" t="s">
         <v>170</v>
@@ -3693,10 +3702,10 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B45">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -3705,21 +3714,21 @@
         <v>167</v>
       </c>
       <c r="E45" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G45">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H45" s="1">
-        <v>45586</v>
+        <v>45579</v>
       </c>
       <c r="K45" t="s">
         <v>163</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="M45" t="s">
         <v>169</v>
       </c>
       <c r="N45" t="s">
@@ -3729,7 +3738,7 @@
         <v>302</v>
       </c>
       <c r="P45" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q45" t="s">
         <v>170</v>
@@ -3740,10 +3749,10 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B46">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -3752,21 +3761,21 @@
         <v>167</v>
       </c>
       <c r="E46" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G46">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H46" s="1">
-        <v>45593</v>
+        <v>45586</v>
       </c>
       <c r="K46" t="s">
         <v>163</v>
       </c>
-      <c r="M46" t="s">
+      <c r="M46" s="2" t="s">
         <v>169</v>
       </c>
       <c r="N46" t="s">
@@ -3776,7 +3785,7 @@
         <v>302</v>
       </c>
       <c r="P46" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q46" t="s">
         <v>170</v>
@@ -3787,10 +3796,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B47">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -3799,16 +3808,16 @@
         <v>167</v>
       </c>
       <c r="E47" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F47" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G47">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H47" s="1">
-        <v>45600</v>
+        <v>45593</v>
       </c>
       <c r="K47" t="s">
         <v>163</v>
@@ -3823,7 +3832,7 @@
         <v>302</v>
       </c>
       <c r="P47" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q47" t="s">
         <v>170</v>
@@ -3834,10 +3843,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B48">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -3846,16 +3855,16 @@
         <v>167</v>
       </c>
       <c r="E48" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G48">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="H48" s="1">
-        <v>45607</v>
+        <v>45600</v>
       </c>
       <c r="K48" t="s">
         <v>163</v>
@@ -3870,7 +3879,7 @@
         <v>302</v>
       </c>
       <c r="P48" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q48" t="s">
         <v>170</v>
@@ -3881,87 +3890,90 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B49">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C49">
         <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>167</v>
+      </c>
+      <c r="E49" t="s">
+        <v>147</v>
+      </c>
+      <c r="F49" t="s">
+        <v>184</v>
+      </c>
+      <c r="G49">
+        <v>68</v>
       </c>
       <c r="H49" s="1">
-        <v>45282</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>383</v>
+        <v>45607</v>
       </c>
       <c r="K49" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="M49" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="N49" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="O49" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="P49" t="s">
-        <v>317</v>
+        <v>369</v>
       </c>
       <c r="Q49" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="R49" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B50">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H50" s="1">
-        <v>45156</v>
+        <v>45282</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K50" t="s">
         <v>18</v>
       </c>
       <c r="M50" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N50" t="s">
         <v>20</v>
       </c>
       <c r="O50" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q50" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="R50" t="s">
         <v>22</v>
@@ -3969,60 +3981,54 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B51">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>194</v>
-      </c>
-      <c r="E51" t="s">
-        <v>122</v>
-      </c>
-      <c r="F51" t="s">
-        <v>195</v>
-      </c>
-      <c r="G51">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="H51" s="1">
-        <v>45631</v>
+        <v>45156</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="K51" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="M51" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N51" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="O51" t="s">
+        <v>294</v>
       </c>
       <c r="P51" t="s">
-        <v>370</v>
+        <v>318</v>
       </c>
       <c r="Q51" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="R51" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B52">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52">
         <v>51</v>
@@ -4031,13 +4037,13 @@
         <v>194</v>
       </c>
       <c r="E52" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F52" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G52">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H52" s="1">
         <v>45631</v>
@@ -4058,7 +4064,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q52" t="s">
         <v>198</v>
@@ -4069,10 +4075,10 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B53">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -4081,16 +4087,16 @@
         <v>194</v>
       </c>
       <c r="E53" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F53" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G53">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H53" s="1">
-        <v>45638</v>
+        <v>45631</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>379</v>
@@ -4108,7 +4114,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q53" t="s">
         <v>198</v>
@@ -4119,10 +4125,10 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B54">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -4131,16 +4137,16 @@
         <v>194</v>
       </c>
       <c r="E54" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F54" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G54">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H54" s="1">
-        <v>45645</v>
+        <v>45638</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>379</v>
@@ -4158,7 +4164,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q54" t="s">
         <v>198</v>
@@ -4169,10 +4175,10 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B55">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -4181,16 +4187,16 @@
         <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F55" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G55">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H55" s="1">
-        <v>45652</v>
+        <v>45645</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>379</v>
@@ -4208,7 +4214,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q55" t="s">
         <v>198</v>
@@ -4219,10 +4225,10 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B56">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -4231,16 +4237,16 @@
         <v>194</v>
       </c>
       <c r="E56" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F56" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G56">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H56" s="1">
-        <v>45659</v>
+        <v>45652</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>379</v>
@@ -4258,7 +4264,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q56" t="s">
         <v>198</v>
@@ -4269,10 +4275,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B57">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -4281,16 +4287,16 @@
         <v>194</v>
       </c>
       <c r="E57" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F57" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G57">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H57" s="1">
-        <v>45666</v>
+        <v>45659</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>379</v>
@@ -4308,7 +4314,7 @@
         <v>125</v>
       </c>
       <c r="P57" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q57" t="s">
         <v>198</v>
@@ -4319,107 +4325,107 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B58">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58">
         <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>29</v>
+        <v>194</v>
+      </c>
+      <c r="E58" t="s">
+        <v>144</v>
+      </c>
+      <c r="F58" t="s">
+        <v>210</v>
       </c>
       <c r="G58">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="H58" s="1">
-        <v>45849</v>
-      </c>
-      <c r="I58" s="3">
-        <v>45796</v>
-      </c>
-      <c r="J58" s="3">
-        <v>45801</v>
+        <v>45666</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="K58" t="s">
         <v>196</v>
       </c>
       <c r="M58" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="N58" t="s">
-        <v>20</v>
-      </c>
-      <c r="O58" t="s">
-        <v>296</v>
+        <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="Q58" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="R58" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B59">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
-      </c>
-      <c r="E59" t="s">
-        <v>215</v>
-      </c>
-      <c r="F59" t="s">
-        <v>216</v>
+        <v>29</v>
       </c>
       <c r="G59">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="H59" s="1">
-        <v>45890</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>380</v>
+        <v>45849</v>
+      </c>
+      <c r="I59" s="3">
+        <v>45796</v>
+      </c>
+      <c r="J59" s="3">
+        <v>45801</v>
       </c>
       <c r="K59" t="s">
         <v>196</v>
       </c>
       <c r="M59" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="N59" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="O59" t="s">
+        <v>296</v>
       </c>
       <c r="P59" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="Q59" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="R59" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B60">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C60">
         <v>59</v>
@@ -4428,19 +4434,19 @@
         <v>121</v>
       </c>
       <c r="E60" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F60" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G60">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H60" s="1">
-        <v>45897</v>
+        <v>45890</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>380</v>
@@ -4455,7 +4461,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q60" t="s">
         <v>218</v>
@@ -4466,10 +4472,10 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B61">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -4478,16 +4484,16 @@
         <v>121</v>
       </c>
       <c r="E61" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F61" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G61">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H61" s="1">
-        <v>45904</v>
+        <v>45897</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>380</v>
@@ -4505,7 +4511,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q61" t="s">
         <v>218</v>
@@ -4516,10 +4522,10 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B62">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -4528,16 +4534,16 @@
         <v>121</v>
       </c>
       <c r="E62" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F62" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G62">
         <v>39</v>
       </c>
       <c r="H62" s="1">
-        <v>45911</v>
+        <v>45904</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>380</v>
@@ -4555,7 +4561,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q62" t="s">
         <v>218</v>
@@ -4566,10 +4572,10 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B63">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -4578,16 +4584,16 @@
         <v>121</v>
       </c>
       <c r="E63" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F63" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G63">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H63" s="1">
-        <v>45918</v>
+        <v>45911</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>380</v>
@@ -4605,7 +4611,7 @@
         <v>125</v>
       </c>
       <c r="P63" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q63" t="s">
         <v>218</v>
@@ -4616,10 +4622,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B64">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -4628,16 +4634,16 @@
         <v>121</v>
       </c>
       <c r="E64" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F64" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G64">
         <v>37</v>
       </c>
       <c r="H64" s="1">
-        <v>45925</v>
+        <v>45918</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>380</v>
@@ -4655,7 +4661,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q64" t="s">
         <v>218</v>
@@ -4666,10 +4672,10 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B65">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -4678,16 +4684,16 @@
         <v>121</v>
       </c>
       <c r="E65" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F65" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G65">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H65" s="1">
-        <v>45932</v>
+        <v>45925</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>380</v>
@@ -4705,7 +4711,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q65" t="s">
         <v>218</v>
@@ -4716,10 +4722,10 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B66">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -4728,22 +4734,22 @@
         <v>121</v>
       </c>
       <c r="E66" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F66" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G66">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="H66" s="1">
-        <v>45939</v>
+        <v>45932</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K66" t="s">
         <v>196</v>
@@ -4755,7 +4761,7 @@
         <v>125</v>
       </c>
       <c r="P66" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q66" t="s">
         <v>218</v>
@@ -4766,87 +4772,99 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B67">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67">
         <v>66</v>
       </c>
       <c r="D67" t="s">
-        <v>241</v>
+        <v>121</v>
+      </c>
+      <c r="E67" t="s">
+        <v>238</v>
+      </c>
+      <c r="F67" t="s">
+        <v>239</v>
       </c>
       <c r="G67">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="H67" s="1">
-        <v>46199</v>
+        <v>45939</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="K67" t="s">
         <v>196</v>
       </c>
       <c r="M67" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="N67" t="s">
-        <v>20</v>
-      </c>
-      <c r="O67" t="s">
-        <v>297</v>
+        <v>125</v>
       </c>
       <c r="P67" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="Q67" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="R67" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B68">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68" t="s">
-        <v>245</v>
-      </c>
-      <c r="E68" t="s">
-        <v>135</v>
+        <v>241</v>
+      </c>
+      <c r="G68">
+        <v>107</v>
       </c>
       <c r="H68" s="1">
-        <v>46271</v>
+        <v>46199</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>397</v>
       </c>
       <c r="K68" t="s">
         <v>196</v>
       </c>
       <c r="M68" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N68" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="O68" t="s">
+        <v>297</v>
       </c>
       <c r="P68" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="Q68" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="R68" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.45">
@@ -7220,7 +7238,7 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="M45" r:id="rId1" xr:uid="{5644AB62-A977-428F-9FE2-4F7F37CACBD0}"/>
+    <hyperlink ref="M46" r:id="rId1" xr:uid="{5644AB62-A977-428F-9FE2-4F7F37CACBD0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DCU.xlsx
+++ b/DCU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D34C01-240A-4524-8165-F3BAF353636A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E38D8C3-99B8-404F-91B8-3A5EC2556BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="414">
   <si>
     <t>id</t>
   </si>
@@ -1275,6 +1275,9 @@
   </si>
   <si>
     <t>Summer, 2016</t>
+  </si>
+  <si>
+    <t>Lights Out</t>
   </si>
 </sst>
 </file>
@@ -2750,93 +2753,96 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="B25">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>245</v>
+      </c>
+      <c r="E25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" t="s">
+        <v>413</v>
       </c>
       <c r="G25">
-        <v>242</v>
+        <v>54</v>
       </c>
       <c r="H25" s="1">
-        <v>43056</v>
+        <v>46278</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="K25" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="M25" t="s">
-        <v>101</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s">
-        <v>20</v>
-      </c>
-      <c r="O25" t="s">
-        <v>282</v>
+        <v>125</v>
       </c>
       <c r="P25" t="s">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="Q25" t="s">
-        <v>102</v>
+        <v>247</v>
       </c>
       <c r="R25" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B26">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G26">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="H26" s="1">
-        <v>43455</v>
+        <v>43056</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="K26" t="s">
         <v>18</v>
       </c>
       <c r="M26" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N26" t="s">
         <v>20</v>
       </c>
       <c r="O26" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q26" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="R26" t="s">
         <v>22</v>
@@ -2844,46 +2850,46 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B27">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27">
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G27">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H27" s="1">
-        <v>43560</v>
+        <v>43455</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="K27" t="s">
         <v>18</v>
       </c>
       <c r="M27" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="N27" t="s">
         <v>20</v>
       </c>
       <c r="O27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q27" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="R27" t="s">
         <v>22</v>
@@ -2891,46 +2897,46 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C28">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G28">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="H28" s="1">
-        <v>43868</v>
+        <v>43560</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K28" t="s">
         <v>18</v>
       </c>
       <c r="M28" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N28" t="s">
         <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P28" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="Q28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="R28" t="s">
         <v>22</v>
@@ -2938,46 +2944,46 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B29">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G29">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="H29" s="1">
-        <v>44407</v>
+        <v>43868</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="K29" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="M29" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N29" t="s">
         <v>20</v>
       </c>
       <c r="O29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P29" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q29" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="R29" t="s">
         <v>22</v>
@@ -2985,60 +2991,57 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B30">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30">
         <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G30">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="H30" s="1">
-        <v>44574</v>
+        <v>44407</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K30" t="s">
         <v>117</v>
       </c>
       <c r="M30" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="N30" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="O30" t="s">
+        <v>288</v>
       </c>
       <c r="P30" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="Q30" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="R30" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -3047,13 +3050,13 @@
         <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G31">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H31" s="1">
         <v>44574</v>
@@ -3074,7 +3077,7 @@
         <v>125</v>
       </c>
       <c r="P31" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q31" t="s">
         <v>126</v>
@@ -3085,10 +3088,10 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B32">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32">
         <v>31</v>
@@ -3097,13 +3100,13 @@
         <v>121</v>
       </c>
       <c r="E32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H32" s="1">
         <v>44574</v>
@@ -3124,7 +3127,7 @@
         <v>125</v>
       </c>
       <c r="P32" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q32" t="s">
         <v>126</v>
@@ -3135,10 +3138,10 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -3147,16 +3150,16 @@
         <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F33" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G33">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H33" s="1">
-        <v>44581</v>
+        <v>44574</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>395</v>
@@ -3174,7 +3177,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q33" t="s">
         <v>126</v>
@@ -3185,10 +3188,10 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B34">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34">
         <v>33</v>
@@ -3197,16 +3200,16 @@
         <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F34" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G34">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H34" s="1">
-        <v>44588</v>
+        <v>44581</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>395</v>
@@ -3224,7 +3227,7 @@
         <v>125</v>
       </c>
       <c r="P34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q34" t="s">
         <v>126</v>
@@ -3235,10 +3238,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B35">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C35">
         <v>34</v>
@@ -3247,16 +3250,16 @@
         <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G35">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H35" s="1">
-        <v>44595</v>
+        <v>44588</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>395</v>
@@ -3274,7 +3277,7 @@
         <v>125</v>
       </c>
       <c r="P35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q35" t="s">
         <v>126</v>
@@ -3285,10 +3288,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B36">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C36">
         <v>35</v>
@@ -3297,16 +3300,16 @@
         <v>121</v>
       </c>
       <c r="E36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F36" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G36">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H36" s="1">
-        <v>44602</v>
+        <v>44595</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>395</v>
@@ -3324,7 +3327,7 @@
         <v>125</v>
       </c>
       <c r="P36" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q36" t="s">
         <v>126</v>
@@ -3335,10 +3338,10 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B37">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C37">
         <v>36</v>
@@ -3347,16 +3350,16 @@
         <v>121</v>
       </c>
       <c r="E37" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F37" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G37">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H37" s="1">
-        <v>44609</v>
+        <v>44602</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>395</v>
@@ -3374,7 +3377,7 @@
         <v>125</v>
       </c>
       <c r="P37" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q37" t="s">
         <v>126</v>
@@ -3385,87 +3388,93 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B38">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C38">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>150</v>
+        <v>121</v>
+      </c>
+      <c r="E38" t="s">
+        <v>147</v>
+      </c>
+      <c r="F38" t="s">
+        <v>148</v>
+      </c>
+      <c r="G38">
+        <v>45</v>
       </c>
       <c r="H38" s="1">
-        <v>44855</v>
+        <v>44609</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="K38" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="M38" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="N38" t="s">
-        <v>20</v>
-      </c>
-      <c r="O38" t="s">
-        <v>290</v>
+        <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="Q38" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="R38" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B39">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C39">
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H39" s="1">
-        <v>45002</v>
+        <v>44855</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K39" t="s">
         <v>18</v>
       </c>
       <c r="M39" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N39" t="s">
         <v>20</v>
       </c>
       <c r="O39" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P39" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="Q39" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="R39" t="s">
         <v>22</v>
@@ -3473,43 +3482,43 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B40">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40">
         <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H40" s="1">
-        <v>45093</v>
+        <v>45002</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K40" t="s">
         <v>18</v>
       </c>
       <c r="M40" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N40" t="s">
         <v>20</v>
       </c>
       <c r="O40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P40" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="Q40" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="R40" t="s">
         <v>22</v>
@@ -3517,43 +3526,43 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B41">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H41" s="1">
-        <v>44624</v>
+        <v>45093</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K41" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="M41" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="N41" t="s">
         <v>20</v>
       </c>
       <c r="O41" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="P41" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q41" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="R41" t="s">
         <v>22</v>
@@ -3561,57 +3570,54 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B42">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>167</v>
-      </c>
-      <c r="E42" t="s">
-        <v>122</v>
-      </c>
-      <c r="F42" t="s">
-        <v>168</v>
-      </c>
-      <c r="G42">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="H42" s="1">
-        <v>45555</v>
+        <v>44624</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="K42" t="s">
         <v>163</v>
       </c>
       <c r="M42" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N42" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="O42" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="P42" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="Q42" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="R42" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B43">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43">
         <v>42</v>
@@ -3620,16 +3626,16 @@
         <v>167</v>
       </c>
       <c r="E43" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F43" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G43">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H43" s="1">
-        <v>45565</v>
+        <v>45555</v>
       </c>
       <c r="K43" t="s">
         <v>163</v>
@@ -3644,7 +3650,7 @@
         <v>302</v>
       </c>
       <c r="P43" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q43" t="s">
         <v>170</v>
@@ -3655,10 +3661,10 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B44">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C44">
         <v>43</v>
@@ -3667,16 +3673,16 @@
         <v>167</v>
       </c>
       <c r="E44" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G44">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H44" s="1">
-        <v>45572</v>
+        <v>45565</v>
       </c>
       <c r="K44" t="s">
         <v>163</v>
@@ -3691,7 +3697,7 @@
         <v>302</v>
       </c>
       <c r="P44" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q44" t="s">
         <v>170</v>
@@ -3702,10 +3708,10 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B45">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45">
         <v>44</v>
@@ -3714,16 +3720,16 @@
         <v>167</v>
       </c>
       <c r="E45" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G45">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H45" s="1">
-        <v>45579</v>
+        <v>45572</v>
       </c>
       <c r="K45" t="s">
         <v>163</v>
@@ -3738,7 +3744,7 @@
         <v>302</v>
       </c>
       <c r="P45" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q45" t="s">
         <v>170</v>
@@ -3749,10 +3755,10 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B46">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C46">
         <v>45</v>
@@ -3761,21 +3767,21 @@
         <v>167</v>
       </c>
       <c r="E46" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F46" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G46">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H46" s="1">
-        <v>45586</v>
+        <v>45579</v>
       </c>
       <c r="K46" t="s">
         <v>163</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="M46" t="s">
         <v>169</v>
       </c>
       <c r="N46" t="s">
@@ -3785,7 +3791,7 @@
         <v>302</v>
       </c>
       <c r="P46" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q46" t="s">
         <v>170</v>
@@ -3796,10 +3802,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B47">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47">
         <v>46</v>
@@ -3808,21 +3814,21 @@
         <v>167</v>
       </c>
       <c r="E47" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F47" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G47">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H47" s="1">
-        <v>45593</v>
+        <v>45586</v>
       </c>
       <c r="K47" t="s">
         <v>163</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M47" s="2" t="s">
         <v>169</v>
       </c>
       <c r="N47" t="s">
@@ -3832,7 +3838,7 @@
         <v>302</v>
       </c>
       <c r="P47" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q47" t="s">
         <v>170</v>
@@ -3843,10 +3849,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B48">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48">
         <v>47</v>
@@ -3855,16 +3861,16 @@
         <v>167</v>
       </c>
       <c r="E48" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F48" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G48">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H48" s="1">
-        <v>45600</v>
+        <v>45593</v>
       </c>
       <c r="K48" t="s">
         <v>163</v>
@@ -3879,7 +3885,7 @@
         <v>302</v>
       </c>
       <c r="P48" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q48" t="s">
         <v>170</v>
@@ -3890,10 +3896,10 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B49">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49">
         <v>48</v>
@@ -3902,16 +3908,16 @@
         <v>167</v>
       </c>
       <c r="E49" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F49" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G49">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="H49" s="1">
-        <v>45607</v>
+        <v>45600</v>
       </c>
       <c r="K49" t="s">
         <v>163</v>
@@ -3926,7 +3932,7 @@
         <v>302</v>
       </c>
       <c r="P49" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q49" t="s">
         <v>170</v>
@@ -3937,87 +3943,90 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B50">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C50">
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>167</v>
+      </c>
+      <c r="E50" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G50">
+        <v>68</v>
       </c>
       <c r="H50" s="1">
-        <v>45282</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>383</v>
+        <v>45607</v>
       </c>
       <c r="K50" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="M50" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="N50" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="O50" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="P50" t="s">
-        <v>317</v>
+        <v>369</v>
       </c>
       <c r="Q50" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="R50" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B51">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C51">
         <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H51" s="1">
-        <v>45156</v>
+        <v>45282</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K51" t="s">
         <v>18</v>
       </c>
       <c r="M51" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N51" t="s">
         <v>20</v>
       </c>
       <c r="O51" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P51" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q51" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="R51" t="s">
         <v>22</v>
@@ -4025,60 +4034,54 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B52">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C52">
         <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>194</v>
-      </c>
-      <c r="E52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F52" t="s">
-        <v>195</v>
-      </c>
-      <c r="G52">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="H52" s="1">
-        <v>45631</v>
+        <v>45156</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="K52" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="M52" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N52" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="O52" t="s">
+        <v>294</v>
       </c>
       <c r="P52" t="s">
-        <v>370</v>
+        <v>318</v>
       </c>
       <c r="Q52" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="R52" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B53">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C53">
         <v>52</v>
@@ -4087,13 +4090,13 @@
         <v>194</v>
       </c>
       <c r="E53" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F53" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G53">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="1">
         <v>45631</v>
@@ -4114,7 +4117,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q53" t="s">
         <v>198</v>
@@ -4125,10 +4128,10 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B54">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C54">
         <v>53</v>
@@ -4137,16 +4140,16 @@
         <v>194</v>
       </c>
       <c r="E54" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F54" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G54">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H54" s="1">
-        <v>45638</v>
+        <v>45631</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>379</v>
@@ -4164,7 +4167,7 @@
         <v>125</v>
       </c>
       <c r="P54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q54" t="s">
         <v>198</v>
@@ -4175,10 +4178,10 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B55">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C55">
         <v>54</v>
@@ -4187,16 +4190,16 @@
         <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F55" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G55">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H55" s="1">
-        <v>45645</v>
+        <v>45638</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>379</v>
@@ -4214,7 +4217,7 @@
         <v>125</v>
       </c>
       <c r="P55" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q55" t="s">
         <v>198</v>
@@ -4225,10 +4228,10 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B56">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C56">
         <v>55</v>
@@ -4237,16 +4240,16 @@
         <v>194</v>
       </c>
       <c r="E56" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F56" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G56">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H56" s="1">
-        <v>45652</v>
+        <v>45645</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>379</v>
@@ -4264,7 +4267,7 @@
         <v>125</v>
       </c>
       <c r="P56" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q56" t="s">
         <v>198</v>
@@ -4275,10 +4278,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B57">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C57">
         <v>56</v>
@@ -4287,16 +4290,16 @@
         <v>194</v>
       </c>
       <c r="E57" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F57" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G57">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H57" s="1">
-        <v>45659</v>
+        <v>45652</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>379</v>
@@ -4314,7 +4317,7 @@
         <v>125</v>
       </c>
       <c r="P57" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q57" t="s">
         <v>198</v>
@@ -4325,10 +4328,10 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B58">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C58">
         <v>57</v>
@@ -4337,16 +4340,16 @@
         <v>194</v>
       </c>
       <c r="E58" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G58">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H58" s="1">
-        <v>45666</v>
+        <v>45659</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>379</v>
@@ -4364,7 +4367,7 @@
         <v>125</v>
       </c>
       <c r="P58" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q58" t="s">
         <v>198</v>
@@ -4375,107 +4378,107 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B59">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C59">
         <v>58</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>194</v>
+      </c>
+      <c r="E59" t="s">
+        <v>144</v>
+      </c>
+      <c r="F59" t="s">
+        <v>210</v>
       </c>
       <c r="G59">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="H59" s="1">
-        <v>45849</v>
-      </c>
-      <c r="I59" s="3">
-        <v>45796</v>
-      </c>
-      <c r="J59" s="3">
-        <v>45801</v>
+        <v>45666</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="K59" t="s">
         <v>196</v>
       </c>
       <c r="M59" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="N59" t="s">
-        <v>20</v>
-      </c>
-      <c r="O59" t="s">
-        <v>296</v>
+        <v>125</v>
       </c>
       <c r="P59" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="Q59" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="R59" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B60">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C60">
         <v>59</v>
       </c>
       <c r="D60" t="s">
-        <v>121</v>
-      </c>
-      <c r="E60" t="s">
-        <v>215</v>
-      </c>
-      <c r="F60" t="s">
-        <v>216</v>
+        <v>29</v>
       </c>
       <c r="G60">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="H60" s="1">
-        <v>45890</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>380</v>
+        <v>45849</v>
+      </c>
+      <c r="I60" s="3">
+        <v>45796</v>
+      </c>
+      <c r="J60" s="3">
+        <v>45801</v>
       </c>
       <c r="K60" t="s">
         <v>196</v>
       </c>
       <c r="M60" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="N60" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="O60" t="s">
+        <v>296</v>
       </c>
       <c r="P60" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="Q60" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="R60" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B61">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C61">
         <v>60</v>
@@ -4484,19 +4487,19 @@
         <v>121</v>
       </c>
       <c r="E61" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F61" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G61">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H61" s="1">
-        <v>45897</v>
+        <v>45890</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>380</v>
@@ -4511,7 +4514,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q61" t="s">
         <v>218</v>
@@ -4522,10 +4525,10 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B62">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62">
         <v>61</v>
@@ -4534,16 +4537,16 @@
         <v>121</v>
       </c>
       <c r="E62" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F62" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G62">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H62" s="1">
-        <v>45904</v>
+        <v>45897</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>380</v>
@@ -4561,7 +4564,7 @@
         <v>125</v>
       </c>
       <c r="P62" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q62" t="s">
         <v>218</v>
@@ -4572,10 +4575,10 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B63">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C63">
         <v>62</v>
@@ -4584,16 +4587,16 @@
         <v>121</v>
       </c>
       <c r="E63" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F63" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G63">
         <v>39</v>
       </c>
       <c r="H63" s="1">
-        <v>45911</v>
+        <v>45904</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>380</v>
@@ -4611,7 +4614,7 @@
         <v>125</v>
       </c>
       <c r="P63" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q63" t="s">
         <v>218</v>
@@ -4622,10 +4625,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B64">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C64">
         <v>63</v>
@@ -4634,16 +4637,16 @@
         <v>121</v>
       </c>
       <c r="E64" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F64" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G64">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H64" s="1">
-        <v>45918</v>
+        <v>45911</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>380</v>
@@ -4661,7 +4664,7 @@
         <v>125</v>
       </c>
       <c r="P64" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q64" t="s">
         <v>218</v>
@@ -4672,10 +4675,10 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B65">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C65">
         <v>64</v>
@@ -4684,16 +4687,16 @@
         <v>121</v>
       </c>
       <c r="E65" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F65" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G65">
         <v>37</v>
       </c>
       <c r="H65" s="1">
-        <v>45925</v>
+        <v>45918</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>380</v>
@@ -4711,7 +4714,7 @@
         <v>125</v>
       </c>
       <c r="P65" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q65" t="s">
         <v>218</v>
@@ -4722,10 +4725,10 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B66">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C66">
         <v>65</v>
@@ -4734,16 +4737,16 @@
         <v>121</v>
       </c>
       <c r="E66" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F66" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G66">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H66" s="1">
-        <v>45932</v>
+        <v>45925</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>380</v>
@@ -4761,7 +4764,7 @@
         <v>125</v>
       </c>
       <c r="P66" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q66" t="s">
         <v>218</v>
@@ -4772,10 +4775,10 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B67">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C67">
         <v>66</v>
@@ -4784,22 +4787,22 @@
         <v>121</v>
       </c>
       <c r="E67" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F67" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G67">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="H67" s="1">
-        <v>45939</v>
+        <v>45932</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K67" t="s">
         <v>196</v>
@@ -4811,7 +4814,7 @@
         <v>125</v>
       </c>
       <c r="P67" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q67" t="s">
         <v>218</v>
@@ -4822,87 +4825,99 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B68">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C68">
         <v>67</v>
       </c>
       <c r="D68" t="s">
-        <v>241</v>
+        <v>121</v>
+      </c>
+      <c r="E68" t="s">
+        <v>238</v>
+      </c>
+      <c r="F68" t="s">
+        <v>239</v>
       </c>
       <c r="G68">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="H68" s="1">
-        <v>46199</v>
+        <v>45939</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="K68" t="s">
         <v>196</v>
       </c>
       <c r="M68" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="N68" t="s">
-        <v>20</v>
-      </c>
-      <c r="O68" t="s">
-        <v>297</v>
+        <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="Q68" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="R68" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B69">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C69">
         <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>245</v>
-      </c>
-      <c r="E69" t="s">
-        <v>138</v>
+        <v>241</v>
+      </c>
+      <c r="G69">
+        <v>107</v>
       </c>
       <c r="H69" s="1">
-        <v>46278</v>
+        <v>46199</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>397</v>
       </c>
       <c r="K69" t="s">
         <v>196</v>
       </c>
       <c r="M69" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N69" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="O69" t="s">
+        <v>297</v>
       </c>
       <c r="P69" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="Q69" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="R69" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.45">
@@ -4912,9 +4927,6 @@
       <c r="B70">
         <v>69</v>
       </c>
-      <c r="C70">
-        <v>69</v>
-      </c>
       <c r="D70" t="s">
         <v>245</v>
       </c>
@@ -4950,9 +4962,6 @@
       <c r="B71">
         <v>70</v>
       </c>
-      <c r="C71">
-        <v>70</v>
-      </c>
       <c r="D71" t="s">
         <v>245</v>
       </c>
@@ -4988,9 +4997,6 @@
       <c r="B72">
         <v>71</v>
       </c>
-      <c r="C72">
-        <v>71</v>
-      </c>
       <c r="D72" t="s">
         <v>245</v>
       </c>
@@ -5026,9 +5032,6 @@
       <c r="B73">
         <v>72</v>
       </c>
-      <c r="C73">
-        <v>72</v>
-      </c>
       <c r="D73" t="s">
         <v>256</v>
       </c>
@@ -5064,9 +5067,6 @@
       <c r="B74">
         <v>73</v>
       </c>
-      <c r="C74">
-        <v>73</v>
-      </c>
       <c r="D74" t="s">
         <v>260</v>
       </c>
@@ -5100,9 +5100,6 @@
         <v>263</v>
       </c>
       <c r="B75">
-        <v>74</v>
-      </c>
-      <c r="C75">
         <v>74</v>
       </c>
       <c r="D75" t="s">
@@ -7238,7 +7235,7 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="M46" r:id="rId1" xr:uid="{5644AB62-A977-428F-9FE2-4F7F37CACBD0}"/>
+    <hyperlink ref="M47" r:id="rId1" xr:uid="{5644AB62-A977-428F-9FE2-4F7F37CACBD0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DCU.xlsx
+++ b/DCU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E38D8C3-99B8-404F-91B8-3A5EC2556BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5028194C-967F-43BB-999F-E0EFC8D33EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="429">
   <si>
     <t>id</t>
   </si>
@@ -1278,6 +1278,51 @@
   </si>
   <si>
     <t>Lights Out</t>
+  </si>
+  <si>
+    <t>Bad Optics</t>
+  </si>
+  <si>
+    <t>The Jordan Boys' Legacy</t>
+  </si>
+  <si>
+    <t>Dirt and Stars</t>
+  </si>
+  <si>
+    <t>Fall, 2026</t>
+  </si>
+  <si>
+    <t>DCU0075</t>
+  </si>
+  <si>
+    <t>The People v. Gorilla Grodd</t>
+  </si>
+  <si>
+    <t>2027-??-??</t>
+  </si>
+  <si>
+    <t>https://www.themoviedb.org/tv/332083-the-people-v-gorilla-grodd</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/title/tt37738867/</t>
+  </si>
+  <si>
+    <t>DCU0076</t>
+  </si>
+  <si>
+    <t>The Brave and the Bold</t>
+  </si>
+  <si>
+    <t>????-??-??</t>
+  </si>
+  <si>
+    <t>https://www.themoviedb.org/movie/1081004-the-brave-and-the-bold</t>
+  </si>
+  <si>
+    <t>https://www.imdb.com/title/tt26545566/</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-brave-and-the-bold/</t>
   </si>
 </sst>
 </file>
@@ -1677,6 +1722,7 @@
     <col min="10" max="10" width="19.86328125" style="3" customWidth="1"/>
     <col min="13" max="13" width="30.86328125" customWidth="1"/>
     <col min="15" max="15" width="83" customWidth="1"/>
+    <col min="16" max="16" width="40.06640625" customWidth="1"/>
     <col min="17" max="17" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4927,14 +4973,29 @@
       <c r="B70">
         <v>69</v>
       </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
       <c r="D70" t="s">
         <v>245</v>
       </c>
       <c r="E70" t="s">
         <v>141</v>
       </c>
+      <c r="F70" t="s">
+        <v>414</v>
+      </c>
+      <c r="G70">
+        <v>54</v>
+      </c>
       <c r="H70" s="1">
         <v>46285</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>417</v>
       </c>
       <c r="K70" t="s">
         <v>196</v>
@@ -4962,14 +5023,29 @@
       <c r="B71">
         <v>70</v>
       </c>
+      <c r="C71">
+        <v>70</v>
+      </c>
       <c r="D71" t="s">
         <v>245</v>
       </c>
       <c r="E71" t="s">
         <v>144</v>
       </c>
+      <c r="F71" t="s">
+        <v>415</v>
+      </c>
+      <c r="G71">
+        <v>48</v>
+      </c>
       <c r="H71" s="1">
         <v>46292</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>417</v>
       </c>
       <c r="K71" t="s">
         <v>196</v>
@@ -4997,14 +5073,29 @@
       <c r="B72">
         <v>71</v>
       </c>
+      <c r="C72">
+        <v>71</v>
+      </c>
       <c r="D72" t="s">
         <v>245</v>
       </c>
       <c r="E72" t="s">
         <v>147</v>
       </c>
+      <c r="F72" t="s">
+        <v>416</v>
+      </c>
+      <c r="G72">
+        <v>57</v>
+      </c>
       <c r="H72" s="1">
         <v>46299</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>417</v>
       </c>
       <c r="K72" t="s">
         <v>196</v>
@@ -5097,44 +5188,99 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>263</v>
+        <v>418</v>
       </c>
       <c r="B75">
         <v>74</v>
       </c>
       <c r="D75" t="s">
+        <v>419</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="K75" t="s">
+        <v>196</v>
+      </c>
+      <c r="N75" t="s">
+        <v>125</v>
+      </c>
+      <c r="P75" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>421</v>
+      </c>
+      <c r="R75" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>263</v>
+      </c>
+      <c r="B76">
+        <v>75</v>
+      </c>
+      <c r="D76" t="s">
         <v>264</v>
       </c>
-      <c r="H75" s="1">
+      <c r="H76" s="1">
         <v>46801</v>
       </c>
-      <c r="K75" t="s">
+      <c r="K76" t="s">
         <v>163</v>
       </c>
-      <c r="M75" t="s">
+      <c r="M76" t="s">
         <v>265</v>
       </c>
-      <c r="N75" t="s">
+      <c r="N76" t="s">
         <v>20</v>
       </c>
-      <c r="O75" t="s">
+      <c r="O76" t="s">
         <v>300</v>
       </c>
-      <c r="P75" t="s">
+      <c r="P76" t="s">
         <v>337</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="Q76" t="s">
         <v>266</v>
       </c>
-      <c r="R75" t="s">
+      <c r="R76" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="H76" s="1"/>
-    </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="H77" s="1"/>
+      <c r="A77" t="s">
+        <v>423</v>
+      </c>
+      <c r="B77">
+        <v>76</v>
+      </c>
+      <c r="D77" t="s">
+        <v>424</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K77" t="s">
+        <v>196</v>
+      </c>
+      <c r="N77" t="s">
+        <v>20</v>
+      </c>
+      <c r="O77" t="s">
+        <v>428</v>
+      </c>
+      <c r="P77" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>426</v>
+      </c>
+      <c r="R77" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.45">
       <c r="H78" s="1"/>
